--- a/ig/main/ValueSet-jdv-age-de-survenue-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-age-de-survenue-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085851</t>
+    <t>20260911143444</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:51+01:00</t>
+    <t>2026-09-11T14:34:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-age-de-survenue-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-age-de-survenue-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260911143444</t>
+    <t>20260916095452</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:34:44+01:00</t>
+    <t>2026-09-16T09:54:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-age-de-survenue-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-age-de-survenue-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260916095452</t>
+    <t>20260928134048</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:54:52+01:00</t>
+    <t>2026-09-28T13:40:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
